--- a/协作/模板/29-变更记录.xlsx
+++ b/协作/模板/29-变更记录.xlsx
@@ -2100,11 +2100,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"需求,契约,设计,路径,清单,交付物"</formula1>
+    <dataValidation sqref="B2:B121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"需求,契约,设计,路径,清单,交付物,流程,协议"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
-      <formula1>"已完成,待批准"</formula1>
+    <dataValidation sqref="J2:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"已完成,待批准,已生效"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
